--- a/data/trans_orig/P1407-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1407-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de estreñimiento crónico en 2012</t>
+          <t>Población con diagnóstico de estreñimiento crónico en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32753</t>
+          <t>31409</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34062</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>695546</t>
+          <t>695393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664297</t>
+          <t>665641</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>684631</t>
+          <t>685421</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1366457</t>
+          <t>1364970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1386404</t>
+          <t>1386140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31266</t>
+          <t>32335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1012392</t>
+          <t>1013418</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>996525</t>
+          <t>995456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1015025</t>
+          <t>1015954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2013152</t>
+          <t>2012426</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2032024</t>
+          <t>2031817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,77 +1437,77 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15255</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9003</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25677</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>18292</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>11142</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>28239</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15255</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9138</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>25489</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>18292</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>10849</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>28915</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>748572</t>
+          <t>748479</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756621</t>
+          <t>756623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,82 +1545,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>761919</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>751497</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>768171</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1516505</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1506558</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1523655</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>98,81%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>761919</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>751685</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>768036</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1516505</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1505882</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1523948</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25332</t>
+          <t>25434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30351</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>937475</t>
+          <t>938571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>946683</t>
+          <t>946749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1026569</t>
+          <t>1026467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1043004</t>
+          <t>1043078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1969289</t>
+          <t>1969100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1987776</t>
+          <t>1987457</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54651</t>
+          <t>55118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88574</t>
+          <t>89920</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65051</t>
+          <t>65148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101985</t>
+          <t>101316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3407307</t>
+          <t>3408524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3421621</t>
+          <t>3421699</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3465342</t>
+          <t>3463996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3499265</t>
+          <t>3498798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6878709</t>
+          <t>6879378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6915643</t>
+          <t>6915546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de estreñimiento crónico en 2016</t>
+          <t>Población con diagnóstico de estreñimiento crónico en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>15955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22436</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32587</t>
+          <t>32184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>659667</t>
+          <t>658845</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671216</t>
+          <t>670913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>650403</t>
+          <t>650886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>666242</t>
+          <t>665916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1315052</t>
+          <t>1315455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1334533</t>
+          <t>1334272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24834</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25284</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1018132</t>
+          <t>1017225</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1018079</t>
+          <t>1018225</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1034705</t>
+          <t>1034788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2040060</t>
+          <t>2038269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2057209</t>
+          <t>2056103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>751752</t>
+          <t>751073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>758690</t>
+          <t>758691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>769434</t>
+          <t>769462</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>782433</t>
+          <t>782634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1526929</t>
+          <t>1525567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1539822</t>
+          <t>1539797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38407</t>
+          <t>37477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>42382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>926918</t>
+          <t>926870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935824</t>
+          <t>935763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1005372</t>
+          <t>1006302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029306</t>
+          <t>1028416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1937140</t>
+          <t>1938964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1961163</t>
+          <t>1961619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26972</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44793</t>
+          <t>43625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>76735</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59773</t>
+          <t>58722</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96054</t>
+          <t>95206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3367378</t>
+          <t>3368750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3384619</t>
+          <t>3384734</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3467533</t>
+          <t>3467807</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3499749</t>
+          <t>3500917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6842838</t>
+          <t>6843686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6879119</t>
+          <t>6880170</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1407-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1407-Habitat-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11629</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31409</t>
+          <t>31616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14379</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35549</t>
+          <t>34745</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>695393</t>
+          <t>695885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>665641</t>
+          <t>665434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>685421</t>
+          <t>685494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1364970</t>
+          <t>1365774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1386140</t>
+          <t>1386010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32335</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>32048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1013418</t>
+          <t>1012252</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>995456</t>
+          <t>997239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1015954</t>
+          <t>1015793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2012426</t>
+          <t>2013690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2031817</t>
+          <t>2032072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>24643</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28239</t>
+          <t>28425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>748479</t>
+          <t>748424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756623</t>
+          <t>756625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>751497</t>
+          <t>752531</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>768171</t>
+          <t>768792</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1506558</t>
+          <t>1506372</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523655</t>
+          <t>1524366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>25640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>11934</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30540</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>938571</t>
+          <t>938247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>946749</t>
+          <t>946744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1026467</t>
+          <t>1026261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1043078</t>
+          <t>1043077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1969100</t>
+          <t>1970321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1987457</t>
+          <t>1987706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18255</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>56005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89920</t>
+          <t>94767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65148</t>
+          <t>64896</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101316</t>
+          <t>102906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3408524</t>
+          <t>3407684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3421699</t>
+          <t>3421619</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3463996</t>
+          <t>3459149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3498798</t>
+          <t>3497911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6879378</t>
+          <t>6877788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6915546</t>
+          <t>6915798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15955</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>23311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32184</t>
+          <t>32257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>658845</t>
+          <t>658896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670913</t>
+          <t>671026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>650886</t>
+          <t>649528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>665916</t>
+          <t>665568</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1315455</t>
+          <t>1315382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1334272</t>
+          <t>1334660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1017225</t>
+          <t>1017736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1018225</t>
+          <t>1018146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1034788</t>
+          <t>1034365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2038269</t>
+          <t>2040000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2056103</t>
+          <t>2056883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>18068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>751073</t>
+          <t>751959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>758691</t>
+          <t>758696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>769462</t>
+          <t>771396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>782634</t>
+          <t>782444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1525567</t>
+          <t>1526495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1539797</t>
+          <t>1539390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37477</t>
+          <t>37136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>41809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>926870</t>
+          <t>926556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935763</t>
+          <t>935811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1006302</t>
+          <t>1006643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1028416</t>
+          <t>1028704</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1938964</t>
+          <t>1939537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1961619</t>
+          <t>1962297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25600</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43625</t>
+          <t>45510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76735</t>
+          <t>78059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58722</t>
+          <t>58051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95206</t>
+          <t>95174</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3368750</t>
+          <t>3368719</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3384734</t>
+          <t>3384633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3467807</t>
+          <t>3466483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3500917</t>
+          <t>3499032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6843686</t>
+          <t>6843718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6880170</t>
+          <t>6880841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
